--- a/etf_holdings/2026-10-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.10%7,700,000</t>
+          <t>13.16%7,700,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.10%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4980</v>
+        <v>1305</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.46%2,210,000</t>
+          <t>7.55%8,460,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.46%</t>
+          <t>7.55%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2210000</v>
+        <v>8460000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1215</v>
+        <v>4950</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.97%8,460,000</t>
+          <t>7.48%2,210,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>7.48%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8460000</v>
+        <v>2210000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3510</v>
+        <v>161.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.95%2,500,000</t>
+          <t>5.74%52,000,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2500000</v>
+        <v>52000000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>161.5</v>
+        <v>6800</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.69%52,000,000</t>
+          <t>5.18%1,115,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.18%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>52000000</v>
+        <v>1115000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6875</v>
+        <v>5185</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.20%1,115,000</t>
+          <t>4.96%1,400,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.20%</t>
+          <t>4.96%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1115000</v>
+        <v>1400000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4975</v>
+        <v>3440</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.72%1,400,000</t>
+          <t>4.94%2,100,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1400000</v>
+        <v>2100000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.75%2,900,000</t>
+          <t>3.74%2,900,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+9.85%602</t>
+          <t>+3.99%626</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.26%8,000,000</t>
+          <t>3.42%8,000,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.17%930,000</t>
+          <t>3.38%930,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.74%7900</t>
+          <t>+3.96%1050</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>+3.96%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7900</v>
+        <v>1050</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.05%570,000</t>
+          <t>3.09%4,310,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>570000</v>
+        <v>4310000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.12%1010</t>
+          <t>0%7900</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1010</v>
+        <v>7900</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.95%4,310,000</t>
+          <t>3.08%570,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4310000</v>
+        <v>570000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1420</v>
+        <v>1460</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.90%3,010,000</t>
+          <t>3.00%3,010,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2555</v>
+        <v>2540</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:00</t>
+          <t>2026-10-02 19:05:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,33 +1363,33 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2110</v>
+        <v>2085</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.53%1,767,956</t>
+          <t>2.42%1,697,956</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1767956</v>
+        <v>1697956</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,20 +1437,20 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.06%2,800,000</t>
+          <t>2.30%2,824,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2800000</v>
+        <v>2824000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.06%1,600,000</t>
+          <t>2.15%1,600,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.98%1,900,000</t>
+          <t>2.10%1,900,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.10%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.49%1565</t>
+          <t>-3.51%1510</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1565</v>
+        <v>1510</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.91%1,800,000</t>
+          <t>1.86%1,800,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.59%254</t>
+          <t>+2.36%260</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.72%10,000,000</t>
+          <t>1.78%10,000,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0%519</t>
+          <t>+1.35%526</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.99%2,800,000</t>
+          <t>1.01%2,800,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.65%2390</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2390</v>
+        <v>6290</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.86%530,000</t>
+          <t>0.86%200,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>530000</v>
+        <v>200000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>-0.17%295.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6205</v>
+        <v>295.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.84%200,000</t>
+          <t>0.81%4,000,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>200000</v>
+        <v>4000000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.51%296</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>296</v>
+        <v>12145</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.80%4,000,000</t>
+          <t>0.62%75,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>4000000</v>
+        <v>75000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>+5.44%543</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>11835</v>
+        <v>543</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.60%75,000</t>
+          <t>0.56%1,500,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>75000</v>
+        <v>1500000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,25 +2090,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.99%254</t>
+          <t>-3.35%2310</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>254</v>
+        <v>2310</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.55%3,200,000</t>
+          <t>0.55%350,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3200000</v>
+        <v>350000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,34 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3211順達</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.13%394</t>
+          <t>-1.18%251</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>394</v>
+        <v>251</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.53%2,000,000</t>
+          <t>0.55%3,200,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2000000</v>
+        <v>3200000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,34 +2212,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>3211順達</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.53%515</t>
+          <t>-1.13%394</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>515</v>
+        <v>394</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.52%1,500,000</t>
+          <t>0.54%2,000,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:01</t>
+          <t>2026-10-02 19:05:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0%707</t>
+          <t>+9.8%1625</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>707</v>
+        <v>1625</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.38%800,000</t>
+          <t>0.39%350,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>800000</v>
+        <v>350000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,34 +2334,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.2%177.5</t>
+          <t>+1.98%721</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>177.5</v>
+        <v>721</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.36%3,000,000</t>
+          <t>0.39%800,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3000000</v>
+        <v>800000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>2882國泰金</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.67%1480</t>
+          <t>+0.9%111.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1480</v>
+        <v>111.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.35%350,000</t>
+          <t>0.30%4,000,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>350000</v>
+        <v>4000000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,34 +2456,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2882國泰金</t>
+          <t>2481強茂</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.45%110.5</t>
+          <t>-1.69%174.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>110.5</v>
+        <v>174.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.30%4,000,000</t>
+          <t>0.24%2,000,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+3.84%1000</t>
+          <t>+1.5%1015</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+3.84%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>+6.23%580</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+6.23%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2080</v>
+        <v>580</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.13%95,000</t>
+          <t>0.12%300,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>95000</v>
+        <v>300000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.09%546</t>
+          <t>+1.06%238</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>546</v>
+        <v>238</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.11%300,000</t>
+          <t>0.06%350,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>300000</v>
+        <v>350000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.21%235.5</t>
+          <t>-1.05%281.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>235.5</v>
+        <v>281.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.06%350,000</t>
+          <t>0.06%300,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>1717長興</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.79%284.5</t>
+          <t>+0.95%74.2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>284.5</v>
+        <v>74.2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.06%300,000</t>
+          <t>0.05%900,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>300000</v>
+        <v>900000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.68%73.5</t>
+          <t>+2.02%505</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>73.5</v>
+        <v>505</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.04%900,000</t>
+          <t>0.02%50,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>900000</v>
+        <v>50000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.02%505</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>505</v>
+        <v>2190</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.03%100,000</t>
+          <t>0.02%15,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>100000</v>
+        <v>15000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.22%121</t>
+          <t>+0.83%122</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.91%602</t>
+          <t>+2.66%618</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:02</t>
+          <t>2026-10-02 19:05:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.04%292.5</t>
+          <t>+5.3%308</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>292.5</v>
+        <v>308</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:04</t>
+          <t>2026-10-02 19:05:39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%335</t>
+          <t>-0.75%332.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>335</v>
+        <v>332.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:04</t>
+          <t>2026-10-02 19:05:39</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.16%1305</t>
+          <t>-1.53%1285</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1305</v>
+        <v>1285</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:04</t>
+          <t>2026-10-02 19:05:39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.27%5490</t>
+          <t>+1.64%5580</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5490</v>
+        <v>5580</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:04</t>
+          <t>2026-10-02 19:05:39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.28%180</t>
+          <t>-0.56%179</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:04</t>
+          <t>2026-10-02 19:05:39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:35</t>
+          <t>2026-10-02 22:50:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:36</t>
+          <t>2026-10-02 22:50:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:37</t>
+          <t>2026-10-02 22:50:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:39</t>
+          <t>2026-10-02 22:50:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:39</t>
+          <t>2026-10-02 22:50:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:39</t>
+          <t>2026-10-02 22:50:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:39</t>
+          <t>2026-10-02 22:50:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:39</t>
+          <t>2026-10-02 22:50:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:00</t>
+          <t>2026-10-02 22:58:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:01</t>
+          <t>2026-10-02 22:58:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:02</t>
+          <t>2026-10-02 22:58:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:03</t>
+          <t>2026-10-02 22:58:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:03</t>
+          <t>2026-10-02 22:58:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:03</t>
+          <t>2026-10-02 22:58:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:03</t>
+          <t>2026-10-02 22:58:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:03</t>
+          <t>2026-10-02 22:58:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:41</t>
+          <t>2026-10-02 23:48:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:42</t>
+          <t>2026-10-02 23:48:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:43</t>
+          <t>2026-10-02 23:48:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:44</t>
+          <t>2026-10-02 23:48:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:44</t>
+          <t>2026-10-02 23:48:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:44</t>
+          <t>2026-10-02 23:48:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:44</t>
+          <t>2026-10-02 23:48:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:44</t>
+          <t>2026-10-02 23:48:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
